--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Styles/UsingRichText.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Styles/UsingRichText.xlsx
@@ -114,7 +114,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -126,6 +126,13 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Styles/UsingRichText.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Styles/UsingRichText.xlsx
@@ -479,7 +479,7 @@
   <x:dimension ref="A1:B3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26.820625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26.250625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="15.410625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Styles/UsingRichText.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Styles/UsingRichText.xlsx
@@ -479,8 +479,8 @@
   <x:dimension ref="A1:B3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26.250625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="15.410625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22.520625000000003" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.060625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Styles/UsingRichText.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Styles/UsingRichText.xlsx
@@ -165,19 +165,19 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Styles/UsingRichText.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Styles/UsingRichText.xlsx
@@ -479,7 +479,7 @@
   <x:dimension ref="A1:B3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22.520625000000003" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22.520625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.060625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
